--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roster" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Roster" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2026 Stats" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Roster'!$A$1:$J$35</definedName>
@@ -22,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -98,8 +99,17 @@
       <color rgb="FF888888"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -220,6 +230,16 @@
         <bgColor rgb="FFFFF4EA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A3A5C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -255,7 +275,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -748,6 +768,16 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3108,4 +3138,3210 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="77" min="1" max="1"/>
+    <col width="8" customWidth="1" style="77" min="2" max="2"/>
+    <col width="28" customWidth="1" style="77" min="3" max="3"/>
+    <col width="12" customWidth="1" style="77" min="4" max="4"/>
+    <col width="8" customWidth="1" style="77" min="5" max="5"/>
+    <col width="8" customWidth="1" style="77" min="6" max="6"/>
+    <col width="8" customWidth="1" style="77" min="7" max="7"/>
+    <col width="8" customWidth="1" style="77" min="8" max="8"/>
+    <col width="8" customWidth="1" style="77" min="9" max="9"/>
+    <col width="8" customWidth="1" style="77" min="10" max="10"/>
+    <col width="8" customWidth="1" style="77" min="11" max="11"/>
+    <col width="8" customWidth="1" style="77" min="12" max="12"/>
+    <col width="8" customWidth="1" style="77" min="13" max="13"/>
+    <col width="8" customWidth="1" style="77" min="14" max="14"/>
+    <col width="18" customWidth="1" style="77" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="165" t="inlineStr">
+        <is>
+          <t>⚾  HITTERS — 2026 Stats</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="166" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B2" s="166" t="inlineStr">
+        <is>
+          <t>Pos</t>
+        </is>
+      </c>
+      <c r="C2" s="166" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D2" s="166" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="E2" s="166" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="F2" s="166" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="G2" s="166" t="inlineStr">
+        <is>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="H2" s="166" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I2" s="166" t="inlineStr">
+        <is>
+          <t>RBI</t>
+        </is>
+      </c>
+      <c r="J2" s="166" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K2" s="166" t="inlineStr">
+        <is>
+          <t>SB</t>
+        </is>
+      </c>
+      <c r="L2" s="166" t="inlineStr">
+        <is>
+          <t>OBP</t>
+        </is>
+      </c>
+      <c r="M2" s="166" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="N2" s="166" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="O2" s="166" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="167" t="inlineStr">
+        <is>
+          <t>Cal Raleigh</t>
+        </is>
+      </c>
+      <c r="B3" s="167" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C3" s="168" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="D3" s="168" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="E3" s="168" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" s="168" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G3" s="168" t="inlineStr">
+        <is>
+          <t>.091</t>
+        </is>
+      </c>
+      <c r="H3" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K3" s="168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" s="168" t="inlineStr">
+        <is>
+          <t>.231</t>
+        </is>
+      </c>
+      <c r="M3" s="168" t="inlineStr">
+        <is>
+          <t>.091</t>
+        </is>
+      </c>
+      <c r="N3" s="168" t="inlineStr">
+        <is>
+          <t>.322</t>
+        </is>
+      </c>
+      <c r="O3" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="167" t="inlineStr">
+        <is>
+          <t>Cam Smith</t>
+        </is>
+      </c>
+      <c r="B4" s="167" t="inlineStr">
+        <is>
+          <t>OF/3B</t>
+        </is>
+      </c>
+      <c r="C4" s="168" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="D4" s="168" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="E4" s="168" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="168" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G4" s="168" t="inlineStr">
+        <is>
+          <t>.077</t>
+        </is>
+      </c>
+      <c r="H4" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="168" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" s="168" t="inlineStr">
+        <is>
+          <t>.294</t>
+        </is>
+      </c>
+      <c r="M4" s="168" t="inlineStr">
+        <is>
+          <t>.077</t>
+        </is>
+      </c>
+      <c r="N4" s="168" t="inlineStr">
+        <is>
+          <t>.371</t>
+        </is>
+      </c>
+      <c r="O4" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="167" t="inlineStr">
+        <is>
+          <t>Taylor Walls</t>
+        </is>
+      </c>
+      <c r="B5" s="167" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="C5" s="168" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="D5" s="168" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="E5" s="168" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F5" s="168" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="G5" s="168" t="inlineStr">
+        <is>
+          <t>.220</t>
+        </is>
+      </c>
+      <c r="H5" s="168" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I5" s="168" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J5" s="168" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K5" s="168" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L5" s="168" t="inlineStr">
+        <is>
+          <t>.280</t>
+        </is>
+      </c>
+      <c r="M5" s="168" t="inlineStr">
+        <is>
+          <t>.319</t>
+        </is>
+      </c>
+      <c r="N5" s="168" t="inlineStr">
+        <is>
+          <t>.599</t>
+        </is>
+      </c>
+      <c r="O5" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="167" t="inlineStr">
+        <is>
+          <t>James Tibbs III</t>
+        </is>
+      </c>
+      <c r="B6" s="167" t="inlineStr">
+        <is>
+          <t>OF</t>
+        </is>
+      </c>
+      <c r="C6" s="168" t="inlineStr">
+        <is>
+          <t>Oklahoma City Baseball Club</t>
+        </is>
+      </c>
+      <c r="D6" s="168" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="E6" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K6" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L6" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O6" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="167" t="inlineStr">
+        <is>
+          <t>DJ Stewart</t>
+        </is>
+      </c>
+      <c r="B7" s="167" t="inlineStr">
+        <is>
+          <t>OF</t>
+        </is>
+      </c>
+      <c r="C7" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="168" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="E7" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L7" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O7" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="167" t="inlineStr">
+        <is>
+          <t>Alex Lodise</t>
+        </is>
+      </c>
+      <c r="B8" s="167" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="C8" s="168" t="inlineStr">
+        <is>
+          <t>Rome Emperors</t>
+        </is>
+      </c>
+      <c r="D8" s="168" t="inlineStr">
+        <is>
+          <t>High-A</t>
+        </is>
+      </c>
+      <c r="E8" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L8" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O8" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="167" t="inlineStr">
+        <is>
+          <t>Marco Dinges</t>
+        </is>
+      </c>
+      <c r="B9" s="167" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C9" s="168" t="inlineStr">
+        <is>
+          <t>Carolina Mudcats</t>
+        </is>
+      </c>
+      <c r="D9" s="168" t="inlineStr">
+        <is>
+          <t>High-A</t>
+        </is>
+      </c>
+      <c r="E9" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L9" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O9" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="167" t="inlineStr">
+        <is>
+          <t>Jaime Ferrer</t>
+        </is>
+      </c>
+      <c r="B10" s="167" t="inlineStr">
+        <is>
+          <t>OF</t>
+        </is>
+      </c>
+      <c r="C10" s="168" t="inlineStr">
+        <is>
+          <t>Cedar Rapids Kernels</t>
+        </is>
+      </c>
+      <c r="D10" s="168" t="inlineStr">
+        <is>
+          <t>High-A</t>
+        </is>
+      </c>
+      <c r="E10" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L10" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O10" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="167" t="inlineStr">
+        <is>
+          <t>Gavin Adams</t>
+        </is>
+      </c>
+      <c r="B11" s="167" t="inlineStr">
+        <is>
+          <t>1B/OF</t>
+        </is>
+      </c>
+      <c r="C11" s="168" t="inlineStr">
+        <is>
+          <t>Bradenton Marauders</t>
+        </is>
+      </c>
+      <c r="D11" s="168" t="inlineStr">
+        <is>
+          <t>Low-A</t>
+        </is>
+      </c>
+      <c r="E11" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K11" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L11" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O11" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="167" t="inlineStr">
+        <is>
+          <t>Yoel Tejeda Jr.</t>
+        </is>
+      </c>
+      <c r="B12" s="167" t="inlineStr">
+        <is>
+          <t>OF</t>
+        </is>
+      </c>
+      <c r="C12" s="168" t="inlineStr">
+        <is>
+          <t>Fredericksburg Nationals</t>
+        </is>
+      </c>
+      <c r="D12" s="168" t="inlineStr">
+        <is>
+          <t>Low-A</t>
+        </is>
+      </c>
+      <c r="E12" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K12" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L12" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O12" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="167" t="inlineStr">
+        <is>
+          <t>Colton Vincent</t>
+        </is>
+      </c>
+      <c r="B13" s="167" t="inlineStr">
+        <is>
+          <t>C/OF</t>
+        </is>
+      </c>
+      <c r="C13" s="168" t="inlineStr">
+        <is>
+          <t>Lake Elsinore Storm</t>
+        </is>
+      </c>
+      <c r="D13" s="168" t="inlineStr">
+        <is>
+          <t>Low-A</t>
+        </is>
+      </c>
+      <c r="E13" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L13" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O13" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="167" t="inlineStr">
+        <is>
+          <t>Max Williams</t>
+        </is>
+      </c>
+      <c r="B14" s="167" t="inlineStr">
+        <is>
+          <t>OF</t>
+        </is>
+      </c>
+      <c r="C14" s="168" t="inlineStr">
+        <is>
+          <t>FCL/Jupiter</t>
+        </is>
+      </c>
+      <c r="D14" s="168" t="inlineStr">
+        <is>
+          <t>Rookie</t>
+        </is>
+      </c>
+      <c r="E14" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K14" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L14" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O14" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="167" t="inlineStr">
+        <is>
+          <t>Drew Faurot</t>
+        </is>
+      </c>
+      <c r="B15" s="167" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="C15" s="168" t="inlineStr">
+        <is>
+          <t>FCL/Jupiter</t>
+        </is>
+      </c>
+      <c r="D15" s="168" t="inlineStr">
+        <is>
+          <t>Rookie</t>
+        </is>
+      </c>
+      <c r="E15" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O15" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="167" t="inlineStr">
+        <is>
+          <t>Gage Harrelson</t>
+        </is>
+      </c>
+      <c r="B16" s="167" t="inlineStr">
+        <is>
+          <t>OF</t>
+        </is>
+      </c>
+      <c r="C16" s="168" t="inlineStr">
+        <is>
+          <t>ACL Angels</t>
+        </is>
+      </c>
+      <c r="D16" s="168" t="inlineStr">
+        <is>
+          <t>Rookie</t>
+        </is>
+      </c>
+      <c r="E16" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O16" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="167" t="inlineStr">
+        <is>
+          <t>Jaxson West</t>
+        </is>
+      </c>
+      <c r="B17" s="167" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C17" s="168" t="inlineStr">
+        <is>
+          <t>ACL/AZL</t>
+        </is>
+      </c>
+      <c r="D17" s="168" t="inlineStr">
+        <is>
+          <t>Rookie</t>
+        </is>
+      </c>
+      <c r="E17" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L17" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O17" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="167" t="inlineStr">
+        <is>
+          <t>Robby Martin Jr.</t>
+        </is>
+      </c>
+      <c r="B18" s="167" t="inlineStr">
+        <is>
+          <t>OF</t>
+        </is>
+      </c>
+      <c r="C18" s="168" t="inlineStr">
+        <is>
+          <t>Kane County Cougars</t>
+        </is>
+      </c>
+      <c r="D18" s="168" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="E18" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O18" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="167" t="inlineStr">
+        <is>
+          <t>Drew Mendoza</t>
+        </is>
+      </c>
+      <c r="B19" s="167" t="inlineStr">
+        <is>
+          <t>1B/3B</t>
+        </is>
+      </c>
+      <c r="C19" s="168" t="inlineStr">
+        <is>
+          <t>High Point Rockers</t>
+        </is>
+      </c>
+      <c r="D19" s="168" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="E19" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K19" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O19" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="165" t="inlineStr">
+        <is>
+          <t>🎯  PITCHERS — 2026 Stats</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="166" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B22" s="166" t="inlineStr">
+        <is>
+          <t>Pos</t>
+        </is>
+      </c>
+      <c r="C22" s="166" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D22" s="166" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="E22" s="166" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="F22" s="166" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="G22" s="166" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H22" s="166" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I22" s="166" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="J22" s="166" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="K22" s="166" t="inlineStr">
+        <is>
+          <t>ERA</t>
+        </is>
+      </c>
+      <c r="L22" s="166" t="inlineStr">
+        <is>
+          <t>WHIP</t>
+        </is>
+      </c>
+      <c r="M22" s="166" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="N22" s="166" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="O22" s="166" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="167" t="inlineStr">
+        <is>
+          <t>Luke Weaver</t>
+        </is>
+      </c>
+      <c r="B23" s="167" t="inlineStr">
+        <is>
+          <t>RHP</t>
+        </is>
+      </c>
+      <c r="C23" s="168" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="D23" s="168" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="E23" s="168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F23" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="168" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="K23" s="168" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L23" s="168" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="M23" s="168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N23" s="168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O23" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="167" t="inlineStr">
+        <is>
+          <t>Tyler Holton</t>
+        </is>
+      </c>
+      <c r="B24" s="167" t="inlineStr">
+        <is>
+          <t>LHP</t>
+        </is>
+      </c>
+      <c r="C24" s="168" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="D24" s="168" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="E24" s="168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F24" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I24" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" s="168" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K24" s="168" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L24" s="168" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="M24" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N24" s="168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O24" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="167" t="inlineStr">
+        <is>
+          <t>Parker Messick</t>
+        </is>
+      </c>
+      <c r="B25" s="167" t="inlineStr">
+        <is>
+          <t>LHP</t>
+        </is>
+      </c>
+      <c r="C25" s="168" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="D25" s="168" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="E25" s="168" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F25" s="168" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G25" s="168" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" s="168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I25" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="168" t="inlineStr">
+        <is>
+          <t>39.2</t>
+        </is>
+      </c>
+      <c r="K25" s="168" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="L25" s="168" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="M25" s="168" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N25" s="168" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O25" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="167" t="inlineStr">
+        <is>
+          <t>Cole Sands</t>
+        </is>
+      </c>
+      <c r="B26" s="167" t="inlineStr">
+        <is>
+          <t>RHP</t>
+        </is>
+      </c>
+      <c r="C26" s="168" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="D26" s="168" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="E26" s="168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" s="168" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K26" s="168" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L26" s="168" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="M26" s="168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N26" s="168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O26" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="167" t="inlineStr">
+        <is>
+          <t>Shane Drohan</t>
+        </is>
+      </c>
+      <c r="B27" s="167" t="inlineStr">
+        <is>
+          <t>LHP</t>
+        </is>
+      </c>
+      <c r="C27" s="168" t="inlineStr">
+        <is>
+          <t>Nashville Sounds</t>
+        </is>
+      </c>
+      <c r="D27" s="168" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="E27" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K27" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L27" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O27" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="167" t="inlineStr">
+        <is>
+          <t>CJ Van Eyk</t>
+        </is>
+      </c>
+      <c r="B28" s="167" t="inlineStr">
+        <is>
+          <t>RHP</t>
+        </is>
+      </c>
+      <c r="C28" s="168" t="inlineStr">
+        <is>
+          <t>Buffalo Bisons</t>
+        </is>
+      </c>
+      <c r="D28" s="168" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="E28" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K28" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L28" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O28" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="167" t="inlineStr">
+        <is>
+          <t>Brandon Leibrandt</t>
+        </is>
+      </c>
+      <c r="B29" s="167" t="inlineStr">
+        <is>
+          <t>LHP</t>
+        </is>
+      </c>
+      <c r="C29" s="168" t="inlineStr">
+        <is>
+          <t>Louisville Bats</t>
+        </is>
+      </c>
+      <c r="D29" s="168" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="E29" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K29" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L29" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O29" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="167" t="inlineStr">
+        <is>
+          <t>Drew Parrish</t>
+        </is>
+      </c>
+      <c r="B30" s="167" t="inlineStr">
+        <is>
+          <t>LHP</t>
+        </is>
+      </c>
+      <c r="C30" s="168" t="inlineStr">
+        <is>
+          <t>Louisville Bats</t>
+        </is>
+      </c>
+      <c r="D30" s="168" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="E30" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K30" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L30" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O30" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="167" t="inlineStr">
+        <is>
+          <t>Jamie Arnold</t>
+        </is>
+      </c>
+      <c r="B31" s="167" t="inlineStr">
+        <is>
+          <t>LHP</t>
+        </is>
+      </c>
+      <c r="C31" s="168" t="inlineStr">
+        <is>
+          <t>Midland RockHounds</t>
+        </is>
+      </c>
+      <c r="D31" s="168" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="E31" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K31" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L31" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O31" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="167" t="inlineStr">
+        <is>
+          <t>Jackson Baumeister</t>
+        </is>
+      </c>
+      <c r="B32" s="167" t="inlineStr">
+        <is>
+          <t>RHP</t>
+        </is>
+      </c>
+      <c r="C32" s="168" t="inlineStr">
+        <is>
+          <t>Montgomery Biscuits</t>
+        </is>
+      </c>
+      <c r="D32" s="168" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="E32" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L32" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O32" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="167" t="inlineStr">
+        <is>
+          <t>Jack Anderson</t>
+        </is>
+      </c>
+      <c r="B33" s="167" t="inlineStr">
+        <is>
+          <t>RHP</t>
+        </is>
+      </c>
+      <c r="C33" s="168" t="inlineStr">
+        <is>
+          <t>Portland Sea Dogs</t>
+        </is>
+      </c>
+      <c r="D33" s="168" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="E33" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K33" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L33" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M33" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N33" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O33" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="167" t="inlineStr">
+        <is>
+          <t>J.C. Flowers</t>
+        </is>
+      </c>
+      <c r="B34" s="167" t="inlineStr">
+        <is>
+          <t>RHP</t>
+        </is>
+      </c>
+      <c r="C34" s="168" t="inlineStr">
+        <is>
+          <t>Altoona Curve</t>
+        </is>
+      </c>
+      <c r="D34" s="168" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="E34" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L34" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O34" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="167" t="inlineStr">
+        <is>
+          <t>Carson Dorsey</t>
+        </is>
+      </c>
+      <c r="B35" s="167" t="inlineStr">
+        <is>
+          <t>LHP</t>
+        </is>
+      </c>
+      <c r="C35" s="168" t="inlineStr">
+        <is>
+          <t>Aberdeen IronBirds</t>
+        </is>
+      </c>
+      <c r="D35" s="168" t="inlineStr">
+        <is>
+          <t>High-A</t>
+        </is>
+      </c>
+      <c r="E35" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J35" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K35" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L35" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O35" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="167" t="inlineStr">
+        <is>
+          <t>Wyatt Crowell</t>
+        </is>
+      </c>
+      <c r="B36" s="167" t="inlineStr">
+        <is>
+          <t>LHP</t>
+        </is>
+      </c>
+      <c r="C36" s="168" t="inlineStr">
+        <is>
+          <t>Great Lakes Loons</t>
+        </is>
+      </c>
+      <c r="D36" s="168" t="inlineStr">
+        <is>
+          <t>High-A</t>
+        </is>
+      </c>
+      <c r="E36" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J36" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K36" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L36" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O36" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="167" t="inlineStr">
+        <is>
+          <t>Conner Whittaker</t>
+        </is>
+      </c>
+      <c r="B37" s="167" t="inlineStr">
+        <is>
+          <t>LHP</t>
+        </is>
+      </c>
+      <c r="C37" s="168" t="inlineStr">
+        <is>
+          <t>Lake County Captains</t>
+        </is>
+      </c>
+      <c r="D37" s="168" t="inlineStr">
+        <is>
+          <t>Low-A</t>
+        </is>
+      </c>
+      <c r="E37" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J37" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K37" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L37" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O37" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="167" t="inlineStr">
+        <is>
+          <t>Bryce Hubbart</t>
+        </is>
+      </c>
+      <c r="B38" s="167" t="inlineStr">
+        <is>
+          <t>LHP</t>
+        </is>
+      </c>
+      <c r="C38" s="168" t="inlineStr">
+        <is>
+          <t>Daytona Tortugas</t>
+        </is>
+      </c>
+      <c r="D38" s="168" t="inlineStr">
+        <is>
+          <t>Low-A</t>
+        </is>
+      </c>
+      <c r="E38" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J38" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K38" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L38" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N38" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O38" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="167" t="inlineStr">
+        <is>
+          <t>Carson Montgomery</t>
+        </is>
+      </c>
+      <c r="B39" s="167" t="inlineStr">
+        <is>
+          <t>RHP</t>
+        </is>
+      </c>
+      <c r="C39" s="168" t="inlineStr">
+        <is>
+          <t>Lake Elsinore Storm</t>
+        </is>
+      </c>
+      <c r="D39" s="168" t="inlineStr">
+        <is>
+          <t>Low-A</t>
+        </is>
+      </c>
+      <c r="E39" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J39" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K39" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L39" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M39" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N39" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O39" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="167" t="inlineStr">
+        <is>
+          <t>Joey Volini</t>
+        </is>
+      </c>
+      <c r="B40" s="167" t="inlineStr">
+        <is>
+          <t>LHP</t>
+        </is>
+      </c>
+      <c r="C40" s="168" t="inlineStr">
+        <is>
+          <t>FCL/Jupiter</t>
+        </is>
+      </c>
+      <c r="D40" s="168" t="inlineStr">
+        <is>
+          <t>Rookie</t>
+        </is>
+      </c>
+      <c r="E40" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J40" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K40" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L40" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O40" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="167" t="inlineStr">
+        <is>
+          <t>Cam Leiter</t>
+        </is>
+      </c>
+      <c r="B41" s="167" t="inlineStr">
+        <is>
+          <t>RHP</t>
+        </is>
+      </c>
+      <c r="C41" s="168" t="inlineStr">
+        <is>
+          <t>ACL/AZL</t>
+        </is>
+      </c>
+      <c r="D41" s="168" t="inlineStr">
+        <is>
+          <t>Rookie</t>
+        </is>
+      </c>
+      <c r="E41" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J41" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K41" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L41" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M41" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O41" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="167" t="inlineStr">
+        <is>
+          <t>Peyton Prescott</t>
+        </is>
+      </c>
+      <c r="B42" s="167" t="inlineStr">
+        <is>
+          <t>RHP</t>
+        </is>
+      </c>
+      <c r="C42" s="168" t="inlineStr">
+        <is>
+          <t>ACL/AZL</t>
+        </is>
+      </c>
+      <c r="D42" s="168" t="inlineStr">
+        <is>
+          <t>Rookie</t>
+        </is>
+      </c>
+      <c r="E42" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J42" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K42" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L42" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N42" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O42" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="167" t="inlineStr">
+        <is>
+          <t>Evan Chrest</t>
+        </is>
+      </c>
+      <c r="B43" s="167" t="inlineStr">
+        <is>
+          <t>RHP</t>
+        </is>
+      </c>
+      <c r="C43" s="168" t="inlineStr">
+        <is>
+          <t>ACL/AZL</t>
+        </is>
+      </c>
+      <c r="D43" s="168" t="inlineStr">
+        <is>
+          <t>Rookie</t>
+        </is>
+      </c>
+      <c r="E43" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J43" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K43" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L43" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O43" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="167" t="inlineStr">
+        <is>
+          <t>Maison Martinez</t>
+        </is>
+      </c>
+      <c r="B44" s="167" t="inlineStr">
+        <is>
+          <t>RHP</t>
+        </is>
+      </c>
+      <c r="C44" s="168" t="inlineStr">
+        <is>
+          <t>ACL/AZL</t>
+        </is>
+      </c>
+      <c r="D44" s="168" t="inlineStr">
+        <is>
+          <t>Rookie</t>
+        </is>
+      </c>
+      <c r="E44" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J44" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K44" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L44" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O44" s="168" t="inlineStr">
+        <is>
+          <t>03/29/2026 21:08</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A21:O21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -3273,17 +3273,17 @@
       </c>
       <c r="E3" s="168" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" s="168" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G3" s="168" t="inlineStr">
         <is>
-          <t>.091</t>
+          <t>.143</t>
         </is>
       </c>
       <c r="H3" s="168" t="inlineStr">
@@ -3293,14 +3293,14 @@
       </c>
       <c r="I3" s="168" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" s="168" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J3" s="168" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K3" s="168" t="inlineStr">
         <is>
           <t>1</t>
@@ -3308,22 +3308,22 @@
       </c>
       <c r="L3" s="168" t="inlineStr">
         <is>
-          <t>.231</t>
+          <t>.294</t>
         </is>
       </c>
       <c r="M3" s="168" t="inlineStr">
         <is>
-          <t>.091</t>
+          <t>.214</t>
         </is>
       </c>
       <c r="N3" s="168" t="inlineStr">
         <is>
-          <t>.322</t>
+          <t>.508</t>
         </is>
       </c>
       <c r="O3" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="O4" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="O5" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="O6" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="O7" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="O8" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="O9" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O10" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="O11" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="O12" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="O13" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="O14" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="O15" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="O16" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="O17" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="O18" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="O19" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="O23" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="O24" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="O25" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -4947,7 +4947,7 @@
       </c>
       <c r="O26" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O27" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="O28" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="O29" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="O30" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="O31" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O32" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="O33" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="O34" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="O35" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="O36" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="O37" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="O38" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="O39" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="O40" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="O41" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="O42" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="O43" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="O44" s="168" t="inlineStr">
         <is>
-          <t>03/29/2026 21:08</t>
+          <t>03/30/2026 01:34</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -3323,7 +3323,7 @@
       </c>
       <c r="O3" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -3350,17 +3350,17 @@
       </c>
       <c r="E4" s="168" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F4" s="168" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G4" s="168" t="inlineStr">
         <is>
-          <t>.077</t>
+          <t>.067</t>
         </is>
       </c>
       <c r="H4" s="168" t="inlineStr">
@@ -3385,22 +3385,22 @@
       </c>
       <c r="L4" s="168" t="inlineStr">
         <is>
-          <t>.294</t>
+          <t>.263</t>
         </is>
       </c>
       <c r="M4" s="168" t="inlineStr">
         <is>
-          <t>.077</t>
+          <t>.067</t>
         </is>
       </c>
       <c r="N4" s="168" t="inlineStr">
         <is>
-          <t>.371</t>
+          <t>.330</t>
         </is>
       </c>
       <c r="O4" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="O5" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -3504,57 +3504,57 @@
       </c>
       <c r="E6" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F6" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G6" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.615</t>
         </is>
       </c>
       <c r="H6" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K6" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.643</t>
         </is>
       </c>
       <c r="M6" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="N6" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.105</t>
         </is>
       </c>
       <c r="O6" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="E7" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F7" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G7" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.125</t>
         </is>
       </c>
       <c r="H7" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K7" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.245</t>
         </is>
       </c>
       <c r="M7" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.257</t>
         </is>
       </c>
       <c r="N7" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.502</t>
         </is>
       </c>
       <c r="O7" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -3658,57 +3658,57 @@
       </c>
       <c r="E8" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F8" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G8" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.252</t>
         </is>
       </c>
       <c r="H8" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J8" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K8" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L8" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.294</t>
         </is>
       </c>
       <c r="M8" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.398</t>
         </is>
       </c>
       <c r="N8" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.692</t>
         </is>
       </c>
       <c r="O8" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -3735,57 +3735,57 @@
       </c>
       <c r="E9" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F9" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>172</t>
         </is>
       </c>
       <c r="G9" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.273</t>
         </is>
       </c>
       <c r="H9" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I9" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J9" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K9" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.371</t>
         </is>
       </c>
       <c r="M9" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.483</t>
         </is>
       </c>
       <c r="N9" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.854</t>
         </is>
       </c>
       <c r="O9" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -3812,57 +3812,57 @@
       </c>
       <c r="E10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>319</t>
         </is>
       </c>
       <c r="G10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.216</t>
         </is>
       </c>
       <c r="H10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.296</t>
         </is>
       </c>
       <c r="M10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.339</t>
         </is>
       </c>
       <c r="N10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.635</t>
         </is>
       </c>
       <c r="O10" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="O11" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="O12" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -4043,57 +4043,57 @@
       </c>
       <c r="E13" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F13" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>134</t>
         </is>
       </c>
       <c r="G13" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.179</t>
         </is>
       </c>
       <c r="H13" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J13" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K13" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L13" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.260</t>
         </is>
       </c>
       <c r="M13" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.201</t>
         </is>
       </c>
       <c r="N13" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.461</t>
         </is>
       </c>
       <c r="O13" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="O14" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="O15" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="O16" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="O17" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="O18" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="O19" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="O23" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="O24" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="O25" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -4947,7 +4947,7 @@
       </c>
       <c r="O26" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -4974,57 +4974,57 @@
       </c>
       <c r="E27" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F27" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G27" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H27" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I27" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J27" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="K27" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="L27" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="M27" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67</t>
         </is>
       </c>
       <c r="N27" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O27" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -5051,57 +5051,57 @@
       </c>
       <c r="E28" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F28" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G28" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H28" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I28" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="K28" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="L28" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="M28" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73</t>
         </is>
       </c>
       <c r="N28" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40</t>
         </is>
       </c>
       <c r="O28" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -5128,57 +5128,57 @@
       </c>
       <c r="E29" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F29" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G29" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H29" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I29" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="K29" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="L29" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="M29" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37</t>
         </is>
       </c>
       <c r="N29" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O29" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -5205,57 +5205,57 @@
       </c>
       <c r="E30" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F30" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G30" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H30" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I30" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J30" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="K30" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="L30" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="M30" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N30" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O30" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="O31" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -5359,57 +5359,57 @@
       </c>
       <c r="E32" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F32" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G32" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H32" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I32" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J32" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="K32" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="L32" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="M32" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51</t>
         </is>
       </c>
       <c r="N32" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O32" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -5436,57 +5436,57 @@
       </c>
       <c r="E33" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F33" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G33" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H33" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I33" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J33" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="K33" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="L33" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="M33" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>90</t>
         </is>
       </c>
       <c r="N33" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O33" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -5513,57 +5513,57 @@
       </c>
       <c r="E34" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F34" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G34" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H34" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I34" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J34" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="K34" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="L34" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="M34" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N34" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O34" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="O35" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -5667,57 +5667,57 @@
       </c>
       <c r="E36" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F36" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G36" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H36" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I36" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J36" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="K36" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="L36" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="M36" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>93</t>
         </is>
       </c>
       <c r="N36" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57</t>
         </is>
       </c>
       <c r="O36" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -5744,57 +5744,57 @@
       </c>
       <c r="E37" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F37" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G37" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H37" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I37" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J37" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="K37" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="L37" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="M37" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45</t>
         </is>
       </c>
       <c r="N37" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O37" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -5821,57 +5821,57 @@
       </c>
       <c r="E38" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F38" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G38" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H38" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I38" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="K38" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="L38" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="M38" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43</t>
         </is>
       </c>
       <c r="N38" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23</t>
         </is>
       </c>
       <c r="O38" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="O39" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="O40" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="O41" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="O42" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="O43" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="O44" s="168" t="inlineStr">
         <is>
-          <t>03/30/2026 15:56</t>
+          <t>03/31/2026 01:38</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -3273,17 +3273,17 @@
       </c>
       <c r="E3" s="168" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F3" s="168" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G3" s="168" t="inlineStr">
         <is>
-          <t>.160</t>
+          <t>.138</t>
         </is>
       </c>
       <c r="H3" s="168" t="inlineStr">
@@ -3308,22 +3308,22 @@
       </c>
       <c r="L3" s="168" t="inlineStr">
         <is>
-          <t>.250</t>
+          <t>.242</t>
         </is>
       </c>
       <c r="M3" s="168" t="inlineStr">
         <is>
-          <t>.200</t>
+          <t>.172</t>
         </is>
       </c>
       <c r="N3" s="168" t="inlineStr">
         <is>
-          <t>.450</t>
+          <t>.414</t>
         </is>
       </c>
       <c r="O3" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -3350,17 +3350,17 @@
       </c>
       <c r="E4" s="168" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F4" s="168" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G4" s="168" t="inlineStr">
         <is>
-          <t>.217</t>
+          <t>.222</t>
         </is>
       </c>
       <c r="H4" s="168" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="J4" s="168" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K4" s="168" t="inlineStr">
@@ -3385,22 +3385,22 @@
       </c>
       <c r="L4" s="168" t="inlineStr">
         <is>
-          <t>.379</t>
+          <t>.364</t>
         </is>
       </c>
       <c r="M4" s="168" t="inlineStr">
         <is>
-          <t>.391</t>
+          <t>.370</t>
         </is>
       </c>
       <c r="N4" s="168" t="inlineStr">
         <is>
-          <t>.770</t>
+          <t>.734</t>
         </is>
       </c>
       <c r="O4" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="O5" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -3504,17 +3504,17 @@
       </c>
       <c r="E6" s="168" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F6" s="168" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G6" s="168" t="inlineStr">
         <is>
-          <t>.500</t>
+          <t>.467</t>
         </is>
       </c>
       <c r="H6" s="168" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="J6" s="168" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K6" s="168" t="inlineStr">
@@ -3539,22 +3539,22 @@
       </c>
       <c r="L6" s="168" t="inlineStr">
         <is>
-          <t>.552</t>
+          <t>.529</t>
         </is>
       </c>
       <c r="M6" s="168" t="inlineStr">
         <is>
-          <t>1.192</t>
+          <t>1.067</t>
         </is>
       </c>
       <c r="N6" s="168" t="inlineStr">
         <is>
-          <t>1.744</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="O6" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="O7" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="O8" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="O9" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -3812,57 +3812,57 @@
       </c>
       <c r="E10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.333</t>
         </is>
       </c>
       <c r="H10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.500</t>
         </is>
       </c>
       <c r="M10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.333</t>
         </is>
       </c>
       <c r="N10" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.833</t>
         </is>
       </c>
       <c r="O10" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="O11" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="O12" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="O13" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="O14" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="O15" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="O16" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="O17" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="O18" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="O19" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="O23" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -4743,49 +4743,49 @@
       </c>
       <c r="E24" s="168" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F24" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I24" s="168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" s="168" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="K24" s="168" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L24" s="168" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="M24" s="168" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F24" s="168" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G24" s="168" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H24" s="168" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I24" s="168" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J24" s="168" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="K24" s="168" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L24" s="168" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="M24" s="168" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="N24" s="168" t="inlineStr">
         <is>
           <t>3</t>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="O24" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="O25" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -4947,7 +4947,7 @@
       </c>
       <c r="O26" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O27" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="O28" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="O29" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="O30" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -5282,57 +5282,57 @@
       </c>
       <c r="E31" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F31" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G31" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H31" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I31" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J31" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="K31" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="L31" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="M31" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N31" s="168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O31" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O32" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="O33" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="O34" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="O35" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="O36" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="O37" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="O38" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="O39" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="O40" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="O41" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="O42" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="O43" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="O44" s="168" t="inlineStr">
         <is>
-          <t>04/03/2026 11:26</t>
+          <t>04/04/2026 10:06</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2536,17 +2536,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>384</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>.176</t>
+          <t>.182</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -2571,22 +2571,22 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>.291</t>
+          <t>.296</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>.371</t>
+          <t>.378</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>.662</t>
+          <t>.674</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -2613,17 +2613,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>448</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>.212</t>
+          <t>.214</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2648,22 +2648,22 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>.278</t>
+          <t>.280</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>.385</t>
+          <t>.391</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>.663</t>
+          <t>.671</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -2690,17 +2690,17 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>117</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>349</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>.219</t>
+          <t>.218</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -2730,17 +2730,17 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>.294</t>
+          <t>.292</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>.598</t>
+          <t>.596</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -2767,17 +2767,17 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>479</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>.293</t>
+          <t>.294</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -2797,27 +2797,27 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>.415</t>
+          <t>.417</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>.543</t>
+          <t>.545</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>.958</t>
+          <t>.962</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -2844,17 +2844,17 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>.235</t>
+          <t>.233</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -2879,22 +2879,22 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>.311</t>
+          <t>.310</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>.365</t>
+          <t>.360</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>.676</t>
+          <t>.670</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -3775,12 +3775,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -3800,32 +3800,32 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>173</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>98</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -5084,57 +5084,57 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>4.97</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>35.1</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/05/2026 12:30</t>
+          <t>09/06/2026 12:44</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2536,17 +2536,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>387</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>.182</t>
+          <t>.183</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>.296</t>
+          <t>.297</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>.378</t>
+          <t>.377</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -2613,17 +2613,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>451</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>.214</t>
+          <t>.213</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2648,22 +2648,22 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>.280</t>
+          <t>.278</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>.391</t>
+          <t>.388</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>.671</t>
+          <t>.666</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -2767,17 +2767,17 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>484</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>.294</t>
+          <t>.291</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -2802,22 +2802,22 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>.417</t>
+          <t>.413</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>.545</t>
+          <t>.539</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>.962</t>
+          <t>.952</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -3723,17 +3723,17 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -4853,14 +4853,14 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -4878,22 +4878,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:44</t>
+          <t>09/07/2026 14:56</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/07/2026 14:56</t>
+          <t>09/08/2026 13:25</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2536,17 +2536,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>391</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>.183</t>
+          <t>.184</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>.377</t>
+          <t>.379</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>.674</t>
+          <t>.676</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -2613,32 +2613,32 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>454</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>.213</t>
+          <t>.214</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -2648,22 +2648,22 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>.278</t>
+          <t>.280</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>.388</t>
+          <t>.394</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>.666</t>
+          <t>.674</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -2767,17 +2767,17 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>487</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>.291</t>
+          <t>.292</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>.413</t>
+          <t>.414</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>.539</t>
+          <t>.538</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -2844,17 +2844,17 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>.233</t>
+          <t>.238</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -2879,22 +2879,22 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>.310</t>
+          <t>.316</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>.360</t>
+          <t>.364</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>.670</t>
+          <t>.680</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -4262,32 +4262,32 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>101.1</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>109</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/08/2026 13:25</t>
+          <t>09/09/2026 13:36</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2536,17 +2536,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>394</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>.184</t>
+          <t>.183</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>.379</t>
+          <t>.376</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>.676</t>
+          <t>.673</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -2613,32 +2613,32 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>458</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>.214</t>
+          <t>.216</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -2648,22 +2648,22 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>.280</t>
+          <t>.281</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>.394</t>
+          <t>.402</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>.674</t>
+          <t>.683</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -2767,12 +2767,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>490</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>103</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>.414</t>
+          <t>.415</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>.538</t>
+          <t>.537</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -2844,17 +2844,17 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>.238</t>
+          <t>.236</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>.316</t>
+          <t>.319</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>.364</t>
+          <t>.361</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -3646,22 +3646,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>57</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -3723,22 +3723,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026 13:36</t>
+          <t>09/10/2026 13:27</t>
         </is>
       </c>
     </row>
